--- a/outputs/tables/combined_friction_tables.xlsx
+++ b/outputs/tables/combined_friction_tables.xlsx
@@ -1440,7 +1440,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="78" customHeight="1">
+    <row r="7" ht="128" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Barge</t>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Ice-free (May–Oct)</t>
+          <t>Ice-free months (monthly ice gating)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Blended all-in rate at Bethel-type distance. Decomposition if linehaul/river legs ever split: ocean linehaul 0.00023 (ISER market rate $0.19–0.22/gal over the 1,276-statute-mile Anchorage–Bethel route), river distribution 0.011 (DEC 2007 invoice $0.007/gal per map mile); lightering/terminal $0.8–1.2/gal fixed component currently blended into the rate.</t>
+          <t>Blended all-in rate at Bethel-type distance. Decomposition if linehaul/river legs ever split: ocean linehaul 0.00023 (ISER market rate $0.19–0.22/gal over the 1,276-statute-mile Anchorage–Bethel route), river distribution 0.011 (DEC 2007 invoice $0.007/gal per map mile); lightering/terminal $0.8–1.2/gal fixed component currently blended into the rate. Operators run Jun–Oct in western and northern Alaska; Gulf and Southeast routes are year-round, so the model gates each waterway cell by its monthly sea- and river-ice cover, not by a calendar window.</t>
         </is>
       </c>
     </row>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="78" customHeight="1">
+    <row r="10" ht="90.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>(a) Rates in USD per gallon-mile (2026$), mirroring friction_costs.py. Each rate survived three verification rounds — blind multi-method derivation, web primary-source verification, and local-document verification (ATRI, Econ One, PCE FY2025, NSB, Noatak) — documented in Fuel Cost Blind Derivations.pdf. Gallon-mile normalization makes modes comparable despite a ~1,000× capacity spread (3,000-gal ice-road truck vs. 3M-gal linehaul barge). Rates are operational costs kept strictly separate from the environmental friction surface (baseline 1.0); seasonal availability is enforced by the friction rasters and edge-month weights, not by the rates.</t>
+          <t>(a) Rates in USD per gallon-mile (2026$), mirroring friction_costs.py. Each rate survived three verification rounds — blind multi-method derivation, web primary-source verification, and local-document verification (ATRI, Econ One, PCE FY2025, NSB, Noatak) — documented in the blind-derivation chapters (supplementary/cost-derivations/ (git history, commit b35b730)). Gallon-mile normalization makes modes comparable despite a ~1,000× capacity spread (3,000-gal ice-road truck vs. 3M-gal linehaul barge). Rates are operational costs kept strictly separate from the environmental friction surface (baseline 1.0); seasonal availability is enforced by the friction rasters and edge-month weights, not by the rates.</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D13" s="8" t="n"/>
     </row>
-    <row r="14" ht="40.5" customHeight="1">
+    <row r="14" ht="53" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>barge ↔ overland</t>
@@ -1551,11 +1551,11 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Road-side truck-rack out-loading only (Crowley Bethel rack $0.276 CPI-2026, shaded for margin); barge marine-header intake excluded as already in the all-in barge rate. Keys 205 edges. Was 0.40.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>Road-side truck-rack out-loading only (Crowley Bethel rack $0.276 CPI-2026, shaded for margin); barge marine-header intake excluded as already in the all-in barge rate. Prices 291 edges (BargeRoadTransfer + BargeAirTransfer). Was 0.40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>plane ↔ overland</t>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Road-side tarmac receiving labor + fittings only; aircraft pump and crew excluded as already in the all-in plane charter rate. Was 0.157.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+          <t>Road-side tarmac receiving labor + fittings only; aircraft pump and crew excluded as already in the all-in plane charter rate. Prices 2 edges. Was 0.157.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>overland ↔ ice road</t>
@@ -1585,11 +1585,11 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Road-carriage side of a continuous truck↔ice-road-truck pumped changeover; ice-road pump-in dwell excluded (in the +20% adder). Was 0.25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40.5" customHeight="1">
+          <t>Road-carriage side of a continuous truck↔ice-road-truck pumped changeover; ice-road pump-in dwell excluded (in the +20% adder). Prices 12 edges. Was 0.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65.5" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>barge ↔ ice road</t>
@@ -1602,15 +1602,15 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Thin facility-interface residual only (both incident modes all-in). Keys 8 edges but is NEVER traversed — barge May–Oct vs ice road Jan–Mar, zero month overlap. Completeness only. Was 0.40.</t>
+          <t>Thin facility-interface residual only (both incident modes all-in). Prices 21 edges at North Slope hubs, expected never to be traversed: ice roads run Jan–Mar, barges only in the summer ice-free window (operators Jun–Oct). Zero month overlap was verified on the 8 such edges of an earlier network; recheck when workflow 03 is rerun. Completeness only. Was 0.40.</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
     </row>
-    <row r="18" ht="78" customHeight="1">
+    <row r="18" ht="90.5" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>(b) Storage-free, rate-aware connection fees in USD per gallon (blind re-derivation, blind_derivations/06_connection_costs.md), applied once per modal handoff, direction-insensitive. Each fee bills only handling with no home in a per-mile rate — the road-carriage side, since Road is carriage-only — and excludes the all-in side (barge intake, aircraft pump/crew, ice-road +20% load/unload adder) to avoid double-counting; hub storage is excluded entirely (never a graph node). The retired storage-leg fees are documented in 05_transfer_fees.md. Total path cost ($/gal) = Σ(mode rate × miles) + the matching fee at every modal handoff.</t>
+          <t>(b) Storage-free, rate-aware connection fees in USD per gallon (blind re-derivation, 06_connection_costs.md in supplementary/cost-derivations/ (git history, commit b35b730)), applied once per modal handoff, direction-insensitive. Each fee bills only handling with no home in a per-mile rate — the road-carriage side, since Road is carriage-only — and excludes the all-in side (barge intake, aircraft pump/crew, ice-road +20% load/unload adder) to avoid double-counting; hub storage is excluded entirely (never a graph node). The retired storage-leg fees are documented in 05_transfer_fees.md (same place). Total path cost ($/gal) = Σ(mode rate × miles) + the matching fee at every modal handoff.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
     </row>
-    <row r="22" ht="65.5" customHeight="1">
+    <row r="22" ht="103" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Blind derivations</t>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Fuel Cost Blind Derivations.pdf and blind_derivations/*.md (project root): four blind per-mode rate derivations (01_road, 02_barge, 03_plane, 04_ice_road) with dated verification addenda, plus the transfer-fee chapters 05_transfer_fees.md (through-storage) and 06_connection_costs.md (storage-free, rate-aware). Values encoded in friction_surface/friction_costs.py.
-Link: blind_derivations/ and Fuel Cost Blind Derivations.pdf (in repo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65.5" customHeight="1">
+          <t>The compiled report fuel_cost_blind_derivations.pdf and its chapters supplementary/cost-derivations/*.md, removed from the working tree on 2026-08-14 and kept in git history at commit b35b730: four blind per-mode rate derivations (01_road, 02_barge, 03_plane, 04_ice_road) with dated verification addenda, plus the transfer-fee chapters 05_transfer_fees.md (through-storage) and 06_connection_costs.md (storage-free, rate-aware). Values encoded in source_scripts/friction_surface/friction_costs.py.
+Link: git show b35b730:supplementary/cost-derivations/&lt;chapter&gt;.md ; b35b730:supplementary/cost-verification/fuel_cost_blind_derivations.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>ATRI 2025</t>
@@ -1657,7 +1657,7 @@
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t>American Transportation Research Institute (2025). An Analysis of the Operational Costs of Trucking: 2025 Update. Road-rate build-up (Tables 8/11: $2.260 average / $2.32 specialized per vehicle-mile); Tables 8/9 verified carriage-only (no rack / terminal / loading line) — the basis for keeping road-side handling in the connection fees.
-Link: cost_derivation_resources/ATRI-Operational-Costs-of-Trucking-07-2025.pdf (in repo)</t>
+Link: ATRI-Operational-Costs-of-Trucking-07-2025.pdf (third-party PDF, not redistributed with the repo)</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Econ One Research (B. Pulliam), The State of Alaska's Refining Industry (Alaska DEC / RCA filing). Road rate: Valdez–Fairbanks truck transport $0.20/gal over 364 mi (CPI 2015→2026).
-Link: cost_derivation_resources/6_barry_pulliam-_econ_one_-_the_state_of_alaskas_refining_industry.pdf (in repo)</t>
+Link: 6_barry_pulliam-_econ_one_-_the_state_of_alaskas_refining_industry.pdf (third-party PDF, not redistributed with the repo)</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Alaska Energy Authority, Power Cost Equalization Program: Statistical Report by Community, FY2025 (final, 2026-03-01). Margin-free utility fuel prices and delivered gallons by community; plane revealed-premium anchor and ice-road ~50/50 regime split (Nuiqsut 279,232 vs Atqasuk 274,877 gal).
-Link: cost_derivation_resources/2026.03.01 FY2025 PCE Statistical Report by Community (Final).pdf (in repo)</t>
+Link: 2026.03.01 FY2025 PCE Statistical Report by Community (Final).pdf (third-party PDF, not redistributed with the repo)</t>
         </is>
       </c>
     </row>
@@ -1774,11 +1774,11 @@
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>UIC Oil &amp; Gas Support account of the Feb–Mar 2026 Anaktuvuk Pass emergency fuel haul (uicalaska.com); Northwest Arctic Borough / Native Village of Noatak Winter Fuel Haul System proposal (2012 legislative grant TPS 58673v1: $425K tracked tractor, 3,000–5,000 gal/trip, ~200 trips/season); ASTAR (Arctic Strategic Transportation and Resources) trail study; North Slope Borough FY26-27 budget; Ontario and NWT winter-road analogs incl. Tibbitt-to-Contwoyto.
-Link: https://www.uicalaska.com/2026/04/15/uicogs-emergency-fuel-haul-to-anaktuvuk-pass/ ; cost_derivation_resources/Northwest_Arctic_Borough_Noatak_Winter_Fuel_Haul_System.pdf ; cost_derivation_resources/NorthSlopeBorough-Budget-Book-FY26-27-FINAL-1.pdf (in repo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65.5" customHeight="1">
+Link: https://www.uicalaska.com/2026/04/15/uicogs-emergency-fuel-haul-to-anaktuvuk-pass/ ; Northwest_Arctic_Borough_Noatak_Winter_Fuel_Haul_System.pdf ; NorthSlopeBorough-Budget-Book-FY26-27-FINAL-1.pdf (third-party PDF, not redistributed with the repo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="78" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Crowley Bethel tariff</t>
@@ -1787,11 +1787,11 @@
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Crowley Fuels LLC, Schedule of Terminal Storage and Throughput Rates — Bethel, Alaska (eff. 2022-08-10): Marine Header throughput $0.1500/gal and Truck Rack $0.2500/gal (storage billed separately), CPI-adjusted to 2026$. Basis for the barge↔overland connection fee (road-side rack leg).
-Link: Crowley Fuels Bethel terminal rate sheet (external); figures recorded in blind_derivations/05_transfer_fees.md &amp; 06_connection_costs.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="78" customHeight="1">
+Link: Crowley Fuels Bethel terminal rate sheet (external); figures recorded in 05_transfer_fees.md &amp; 06_connection_costs.md (supplementary/cost-derivations/ (git history, commit b35b730))</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="90.5" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Port tariffs</t>
@@ -1800,7 +1800,7 @@
       <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Port of Bethel Terminal Tariff #5 §206(D) inbound-petroleum wharfage ($0.06/gal, 2026 column); Port of Nome Tariff No. 16.5 §05.020 bulk-liquid wharfage ($0.048/gal) and §05.035 header-crew labor ($115/hr); Port of Alaska Tariff Item 260 fuel-transfer rate. Municipal wharfage / facility-interface cross-checks for the connection fees.
-Link: Port of Bethel Tariff #5 / Port of Nome Tariff 16.5 / Port of Alaska Item 260 (external); figures recorded in blind_derivations/05–06</t>
+Link: Port of Bethel Tariff #5 / Port of Nome Tariff 16.5 / Port of Alaska Item 260 (external); figures recorded in chapters 05–06 (supplementary/cost-derivations/ (git history, commit b35b730))</t>
         </is>
       </c>
     </row>
@@ -1832,10 +1832,10 @@
       <c r="C36" s="9" t="n"/>
       <c r="D36" s="9" t="n"/>
     </row>
-    <row r="37" ht="65.5" customHeight="1">
+    <row r="37" ht="78" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>(c) Full citations, each with a link or locator (a verified public URL, an in-repo file path, or an explicit 'no stable public URL'). The rate sources support the four per-gallon-mile rates; the Crowley, port, Pamphlet-600, ISER and Bristol Bay entries additionally support the storage-free connection fees. Convergence between independent methods — not any single source — is the evidence standard; per-figure page cites live in the blind_derivations chapters.</t>
+          <t>(c) Full citations, each with a link or locator (a verified public URL, a path in this repo's git history, a third-party file that is not redistributed, or an explicit 'no stable public URL'). The rate sources support the four per-gallon-mile rates; the Crowley, port, Pamphlet-600, ISER and Bristol Bay entries additionally support the storage-free connection fees. Convergence between independent methods — not any single source — is the evidence standard; per-figure page cites live in the derivation chapters (supplementary/cost-derivations/ (git history, commit b35b730)).</t>
         </is>
       </c>
     </row>
